--- a/DOC/機能仕様書_壁紙積算システム.xlsx
+++ b/DOC/機能仕様書_壁紙積算システム.xlsx
@@ -513,7 +513,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -558,7 +557,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>Django ソース、テンプレート、管理画面設定、CSV出力処理、マイグレーション0015までを解析して改定</t>
         </is>
       </c>
     </row>
@@ -574,8 +573,13 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>最終改定日: 2026-06-15</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -607,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -769,7 +773,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>案件名、顧客名、図面PDF、面別初期壁紙、図面ページ指定を受け付け、PDF解析結果から部屋明細を作成する。</t>
+          <t>案件名、顧客名、図面PDF、面別初期壁紙、図面ページ指定、表ページ指定を受け付け、PDF解析結果から部屋明細を作成する。</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -784,7 +788,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>PDF必須、10MB以下、MIME application/pdf、先頭%PDF-</t>
+          <t>PDF必須、10MB以下、MIME application/pdf、先頭%PDF-。平面図ページ指定が必要</t>
         </is>
       </c>
     </row>
@@ -833,7 +837,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>指定ページだけを抽出した一時PDFを OpenAI API に渡し、部屋名・寸法・開口・天井面積・面別情報をJSONで取得する。</t>
+          <t>指定ページ・表ページを抽出した一時PDFを OpenAI API に渡し、部屋名・寸法・開口・天井面積・面別情報をJSONで取得する。</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -848,7 +852,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>平面図ページ未指定、範囲外、API未設定はエラー</t>
+          <t>表ページ候補、抽出失敗部屋、解析ステータス/エラーを管理</t>
         </is>
       </c>
     </row>
@@ -897,7 +901,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>案件、壁紙別集計、部屋別明細、採用見積方式、PDFページ指定、注意メモを表示する。</t>
+          <t>案件、壁紙別集計、部屋別明細、採用見積方式、PDF/表ページ指定、解析状態、計算時間、注意メモを表示する。</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -944,7 +948,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>数値不正時は既存値または0に丸める</t>
+          <t>数値不正時は既存値または0に丸める。壁紙無しは集計除外</t>
         </is>
       </c>
     </row>
@@ -1201,6 +1205,70 @@
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>PDFメタ情報とアップロードユーザーは読み取り専用</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>F-018</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>表ページ指定・候補抽出</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>床面積表、居室区画面積表、室内仕上表、内部仕上表、建具表、その他表ページを指定または自動検出し、部屋候補抽出に利用する。</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>_table_pages_from_project / _room_table_candidates</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>案件所有者</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>指定ページは自動検出より優先。その他表ページはカンマ・範囲指定可</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>F-019</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>解析状態管理</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PDF解析の未実行、解析中、解析完了、解析失敗、解析モデル、開始/終了日時、直近計算時間、失敗理由を案件に保持する。</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>_read_pdf_into_project</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>案件所有者</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>失敗時は既存画面にメッセージと解析エラーを表示</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1418,6 +1486,23 @@
       <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CSVの面積は小数第2位へ量子化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>集計対象外</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Room.excluded_from_summary=True の部屋は wallpaper_area、total_area、rolls_required、壁紙別集計の対象外</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>編集画面で部屋単位に指定。CSV部屋別明細には対象外表示を出力。</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1607,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>name, client_name, drawing_pdf*, uploaded_by, adopted_estimate_method, page_*, memo, created_at, updated_at</t>
+          <t>name, client_name, drawing_pdf*, uploaded_by, adopted_estimate_method, page_*, analysis_*, last_calculation_seconds, memo, created_at, updated_at</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>図面PDFのローカル/Storage保存情報とページ指定を保持。</t>
+          <t>図面PDFのローカル/Storage保存情報、図面/表ページ指定、解析状態・エラー・モデル・処理時間を保持。</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1634,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AI読取、抽出失敗、手動追加の区分を保持。</t>
+          <t>AI読取、抽出失敗、手動追加の区分と集計対象外フラグを保持。</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1703,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
